--- a/research/Melbourne_Waste_Skip_Rearlift_GardenBag_Companies.xlsx
+++ b/research/Melbourne_Waste_Skip_Rearlift_GardenBag_Companies.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Melbourne Waste Companies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Research Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Invite Email Template" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Research Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Melbourne Waste Companies'!$A$1:$K$60</definedName>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +38,20 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -88,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -103,6 +118,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3798,6 +3819,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Waste Expo Australia 2026 — WasteVantage invite email</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Waste Expo Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>28 – 29 October 2026, 9am – 5pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Melbourne Convention and Exhibition Centre (MCEC), South Wharf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Expo website</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.wasteexpoaustralia.com.au/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>WasteVantage</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://ihublogistics.com/wastevantage/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>SUBJECT (option 1)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{{Company Name}} — meet WasteVantage at Waste Expo Australia (28–29 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>SUBJECT (option 2)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Invitation: see WasteVantage live at Waste Expo Melbourne, 28–29 October</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>EMAIL BODY — copy below</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="520" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hi {{First Name / team at Company Name}},
+We're writing from WasteVantage to invite you to visit us at Waste Expo Australia 2026.
+When: Wednesday 28 – Thursday 29 October 2026, 9am–5pm
+Where: Melbourne Convention and Exhibition Centre (MCEC)
+Event: https://www.wasteexpoaustralia.com.au/
+Waste Expo is Australia's leading gathering for waste, recycling and resource recovery — with 3,500+ attendees, 140+ exhibitors and free education sessions. It's the best place this year to see what's next for operators like yours.
+WHY VISIT WASTEVANTAGE AT THE EXPO?
+WasteVantage is purpose-built waste management software for Australian and New Zealand operators — including skip bin hire, rearlift / wheelie bin rounds, front lift, and garden / skip bag style services.
+At our stand you can:
+• See a live demo of bookings, dispatch, bin tracking and driver run sheets in one system
+• Talk through your operation (skip delivery/pickup, rearlift schedules, garden bag collections) with people who understand the workflow
+• Compare how you run today vs automating pricing, job scheduling, customer SMS and same-day invoicing
+• Ask about Xero / MYOB / Stripe integrations so office admin and cash flow stay connected
+• Get a clear view of whether WasteVantage fits a single-stream business or a multi-stream fleet (skips + rearlift + bags)
+WHAT WASTEVANTAGE CAN DO FOR {{Company Name}}
+If you're juggling phone bookings, spreadsheets, drivers and invoices, the expo is a low-risk way to see how operators are cutting admin and missed jobs:
+• High volume skip deliveries, pickups and swaps → Smart scheduling &amp; dispatch so jobs aren't missed or double-booked
+• "Where is that bin?" / lost assets → Real-time bin status, location and customer tracking
+• Drivers needing paper run sheets and constant office calls → Automated run sheets on driver phones + live job updates
+• Slow or messy invoicing after jobs close → One-click / same-day invoicing synced to Xero or MYOB
+• Customers chasing ETAs → Automated SMS / notifications and clearer service proof
+• Growing into rearlift or garden bags alongside skips → One platform for multi-stream operations
+Built and supported in Australia for local operators — not a generic overseas logistics tool bolted onto waste.
+WHY COME IN PERSON?
+• Free trade visitor registration for industry professionals via the expo site
+• Face-to-face demo beats a cold website click — bring your toughest operational question
+• See peers and suppliers in one venue while you're there
+• Melbourne timing — ideal if you already service metro Melbourne and surrounds
+If you're free on either day, we'd love 15–20 minutes at our stand to walk you through a demo tailored to skip / rearlift / garden bag work.
+RSVP / book a time: reply to this email with a preferred day (28 or 29 Oct) and we'll hold a slot for {{Company Name}}.
+Expo info &amp; visitor registration: https://www.wasteexpoaustralia.com.au/
+Learn more about WasteVantage: https://ihublogistics.com/wastevantage/
+Looking forward to meeting you in Melbourne.
+Kind regards,
+{{Your Name}}
+{{Your Title}}
+WasteVantage
+{{Your Phone}}
+{{Your Email}}
+https://ihublogistics.com/wastevantage/
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>SHORT FOLLOW-UP SUBJECT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Quick reminder — WasteVantage at Waste Expo (28–29 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>SHORT FOLLOW-UP BODY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="160" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Hi {{First Name}},
+Just a short follow-up on our invite to meet at Waste Expo Australia, 28–29 October 2026 at MCEC Melbourne.
+We'll be showing WasteVantage live — bookings, bin tracking, driver apps and automated invoicing for skip, rearlift and garden bag operators.
+If you're attending, reply with your preferred day and we'll book a 15-minute demo for {{Company Name}}.
+Expo: https://www.wasteexpoaustralia.com.au/
+Thanks,
+{{Your Name}} | WasteVantage</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>SENDING TIPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>1. Replace {{Company Name}} / {{First Name}} from the company list sheet.  2. Add booth/stand number once confirmed.  3. Send one-to-one (not bulk BCC).  4. Confirm exhibitor registration &amp; free visitor entry before promising it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/research/Melbourne_Waste_Skip_Rearlift_GardenBag_Companies.xlsx
+++ b/research/Melbourne_Waste_Skip_Rearlift_GardenBag_Companies.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Melbourne Waste Companies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Invite Email Template" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Research Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Melbourne Waste Companies" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invite Email Template" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Melbourne Waste Companies'!$A$1:$K$60</definedName>
@@ -54,7 +54,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,6 +127,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1071,9 +1079,9 @@
           <t>03 9460 5333</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Not published clearly (see website)</t>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>admin@unlimitedbins.com.au</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1108,7 +1116,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Also unlimitedbins.com.au; email obfuscated on site</t>
+          <t>Email from company contact page / privacy policy | was: Also unlimitedbins.com.au; email obfuscated on site</t>
         </is>
       </c>
     </row>
@@ -1181,9 +1189,9 @@
           <t>03 9005 7675</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Not found publicly (call/book online)</t>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>info@choicebins.com.au</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1218,7 +1226,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Company website; email not listed</t>
+          <t>Email from company contact page | was: Company website; email not listed</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1721,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>No public email found after deep search; phone/office only (03 8872 7879)</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1776,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Company site; CoM waste providers list</t>
+          <t>No public general email found; use phone 1300 219 001 or online form</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2161,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Company website; CoM list</t>
+          <t>No public email found; phone only 03 9824 1975</t>
         </is>
       </c>
     </row>
@@ -2391,9 +2399,9 @@
           <t>1300 550 408</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Not published (contact form)</t>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>contact@wastewise.com.au</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2428,7 +2436,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Company contact page; CoM list</t>
+          <t>Also sales@wastewise.com.au on older site page | was: Company contact page; CoM list</t>
         </is>
       </c>
     </row>
@@ -2501,9 +2509,9 @@
           <t>1300 586 548</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Not published (online booking / form)</t>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>info@aussieskipbags.com.au</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2538,7 +2546,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Also collects Croc Bags; company site</t>
+          <t>Also operations@aussieskipbags.com.au | was: Also collects Croc Bags; company site</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2711,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Melbourne office (03) 8397 5100; CoM list</t>
+          <t>No public general email; use 13 13 39 or online enquiry form</t>
         </is>
       </c>
     </row>
@@ -2721,9 +2729,9 @@
           <t>13 29 55</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Not published (online enquiry form)</t>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>cx.service@anz.veolia.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2758,7 +2766,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>CoM waste providers list</t>
+          <t>Customer experience team email from Veolia ANZ portals page; also call 13 29 55 | was: CoM waste providers list</t>
         </is>
       </c>
     </row>
@@ -2831,9 +2839,9 @@
           <t>13 15 46</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Not published nationally (franchise local)</t>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>jimscontracts@jims.net</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2868,7 +2876,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Franchise model; local franchisees vary</t>
+          <t>Jim's Contracts / national office email; local franchisees may differ — also call 13 15 46 | was: Franchise model; local franchisees vary</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3206,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>Connects to local operators</t>
+          <t>Referral aggregator — no public email on site; phone 0482 392 415</t>
         </is>
       </c>
     </row>
@@ -3216,14 +3224,14 @@
           <t>03 9670 4042</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Not found publicly (call)</t>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>admin@phoenixwastecollection.com.au</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Search company name + Melbourne</t>
+          <t>https://www.phoenixwastecollection.com.au/</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3253,7 +3261,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>City of Melbourne waste providers list</t>
+          <t>Company contact page; also phone 03 9670 4042 | was: City of Melbourne waste providers list</t>
         </is>
       </c>
     </row>
@@ -3271,44 +3279,44 @@
           <t>1300 292 783</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Not found publicly (call)</t>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>sales@awaste.com.au</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Search company name + Melbourne</t>
+          <t>https://www.australianwastemanagement.com.au/</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
+          <t>56 Paraweena Drive, Truganina VIC 3029</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Yes (listed)</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Yes (listed recycling streams)</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Yes (listed)</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>Yes (listed recycling streams)</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>Melbourne</t>
-        </is>
-      </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>City of Melbourne waste providers list</t>
+          <t>Also known as AWASTE; Wyndham directory + company site | was: City of Melbourne waste providers list</t>
         </is>
       </c>
     </row>
@@ -3323,22 +3331,22 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>1300 267 469</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Not found publicly (call)</t>
+          <t>1300 267 4696</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>contactcentre@coriowm.com.au</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Search company name + Geelong/Melbourne</t>
+          <t>https://www.coriowm.com.au/</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Geelong / Melbourne region</t>
+          <t>41-49 Wills Cres, Moolap VIC 3224 (also Altona North &amp; Dandenong South)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3363,7 +3371,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>CoM list (phone shown as 1300 267 4696 on CoM; verify digit count)</t>
+          <t>Also sales@coriowm.com.au; serves Geelong, Ballarat &amp; Melbourne | was: CoM list (phone shown as 1300 267 4696 on CoM; verify digit count)</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3426,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>City of Melbourne waste providers list</t>
+          <t>Brand largely under Veolia; use 131 335 / Veolia channels; no separate public email found</t>
         </is>
       </c>
     </row>
@@ -3436,44 +3444,44 @@
           <t>1300 723 232</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>Not found publicly (call)</t>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>info@waynecleaningsystems.com.au</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Search Wayne Cleaning Systems waste Melbourne</t>
+          <t>https://www.waynecleaningsystems.com.au/</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
+          <t>147 Miller Street / 23 Taylor Street, Thornbury VIC; Waste depot 10 Wentworth Ct, Thomastown</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Listed provider</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Yes (listed streams)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Listed provider</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Yes (listed streams)</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Melbourne</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>City of Melbourne waste providers list</t>
+          <t>Company website contact | was: City of Melbourne waste providers list</t>
         </is>
       </c>
     </row>
@@ -3491,9 +3499,9 @@
           <t>1300 954 576</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Not found publicly (call)</t>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>peter@limitlessrecycling.com.au</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -3503,32 +3511,32 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
+          <t>33 Malua Street, Reservoir VIC</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Listed provider</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Yes (listed)</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Listed provider</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>Yes (listed)</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>Melbourne</t>
-        </is>
-      </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>City of Melbourne waste providers list</t>
+          <t>Recycling Near You directory listing | was: City of Melbourne waste providers list</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3591,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>City of Melbourne waste providers list</t>
+          <t>No public email found; phone only 0406 267 275</t>
         </is>
       </c>
     </row>
@@ -3601,14 +3609,14 @@
           <t>0452 458 909</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Not found publicly (call)</t>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>estimatorvic@aldcorporate.com.au</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Search Expert Demo waste Melbourne</t>
+          <t>https://www.expertdemo.com.au/</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -3638,7 +3646,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>City of Melbourne construction waste providers</t>
+          <t>Expert Demo site lists ALD Corporate VIC estimator email — confirm before outreach; phone 0452 458 909 from CoM list | was: City of Melbourne construction waste providers</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3671,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Search Revert Group Melbourne waste</t>
+          <t>https://revertgroup.com.au/</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3693,7 +3701,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>City of Melbourne construction waste providers</t>
+          <t>No public email on site; phone 1300 307 450 / 0416 416 224 or online form — https://revertgroup.com.au/</t>
         </is>
       </c>
     </row>
@@ -3711,44 +3719,44 @@
           <t>1300 648 088</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Not found publicly (call)</t>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>info@wasteninja.com.au</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Search Waste Ninja Melbourne</t>
+          <t>https://wasteninja.com.au/</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
+          <t>5A Connection Drive, Campbellfield VIC 3061</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Food organics (listed)</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>Food organics (listed)</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>Melbourne</t>
-        </is>
-      </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>City of Melbourne food organics providers</t>
+          <t>Company contact page | was: City of Melbourne food organics providers</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4078,7 +4086,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -4158,6 +4166,181 @@
       <c r="A18" t="inlineStr">
         <is>
           <t>- This list is for research/outreach; not an endorsement. Verify details before use as contacts change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Email enrichment update</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Newly filled emails: 13; still missing public email: 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unlimited Bins (Skip Hire Melbourne)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>admin@unlimitedbins.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Choice Bins</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>info@choicebins.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Waste Wise Environmental</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>contact@wastewise.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Aussie Skip Bags</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>info@aussieskipbags.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Veolia Environmental Services</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cx.service@anz.veolia.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jim's Skip Bins</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>jimscontracts@jims.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Phoenix Environmental Waste</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>admin@phoenixwastecollection.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Australian Waste Management</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sales@awaste.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Corio Waste Management</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>contactcentre@coriowm.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wayne Cleaning Systems</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>info@waynecleaningsystems.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Limitless Secure Recycling &amp; Waste Solutions</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>peter@limitlessrecycling.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Expert Demo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>estimatorvic@aldcorporate.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Waste Ninja</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>info@wasteninja.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Green email cells = newly found in this enrichment pass. Yellow = still no public email (use phone).</t>
         </is>
       </c>
     </row>

--- a/research/Melbourne_Waste_Skip_Rearlift_GardenBag_Companies.xlsx
+++ b/research/Melbourne_Waste_Skip_Rearlift_GardenBag_Companies.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Melbourne Waste Companies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invite Email Template" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIC Waste Companies" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invite Email Template" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Melbourne Waste Companies'!$A$1:$K$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VIC Waste Companies'!$A$1:$L$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,21 +37,8 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -108,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,16 +109,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,23 +478,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No.</t>
@@ -546,25 +528,30 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Region (VIC)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Skip Bin Hire</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Rearlift / Wheelie Bins</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Garden Bags / Skip Bags</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Service Area</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Notes / Source</t>
         </is>
@@ -601,12 +588,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -616,10 +603,15 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>Dandenong &amp; SE Melbourne</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Example company from request; company website</t>
         </is>
@@ -656,12 +648,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -671,10 +663,15 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>Melbourne West &amp; North</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Company contact page</t>
         </is>
@@ -711,12 +708,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -726,10 +723,15 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>Across Melbourne</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Company contact page</t>
         </is>
@@ -766,12 +768,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -781,10 +783,15 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>Melbourne West</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Company website</t>
         </is>
@@ -821,12 +828,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -836,10 +843,15 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>Melbourne metro</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Also management@skipsskipbins.com.au</t>
         </is>
@@ -876,12 +888,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -891,10 +903,15 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
           <t>Greater Melbourne</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Company website</t>
         </is>
@@ -931,12 +948,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -946,10 +963,15 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>Melbourne (also Adelaide/Brisbane)</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Also listed as Kartaway Miniskips on CoM list (03 9326 5555)</t>
         </is>
@@ -986,12 +1008,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Eastern suburbs / Yarra Valley</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1001,10 +1023,15 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
           <t>Eastern suburbs &amp; Yarra Valley</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>Company / LinkedIn contact data</t>
         </is>
@@ -1041,12 +1068,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1056,10 +1083,15 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>Melbourne-wide (based West)</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Hook lift &amp; skip bins; company FAQ</t>
         </is>
@@ -1079,7 +1111,7 @@
           <t>03 9460 5333</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>admin@unlimitedbins.com.au</t>
         </is>
@@ -1096,12 +1128,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1111,10 +1143,15 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
           <t>North, East, SE &amp; West Melbourne</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>Email from company contact page / privacy policy | was: Also unlimitedbins.com.au; email obfuscated on site</t>
         </is>
@@ -1151,12 +1188,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Frankston / Mornington Peninsula</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1166,10 +1203,15 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>Frankston, Mornington, Cranbourne</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Company contact page</t>
         </is>
@@ -1189,7 +1231,7 @@
           <t>03 9005 7675</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>info@choicebins.com.au</t>
         </is>
@@ -1206,25 +1248,30 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
           <t>Green waste accepted in skips</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>Melbourne metro</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Email from company contact page | was: Company website; email not listed</t>
         </is>
@@ -1261,25 +1308,30 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>Yes (commercial)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>Melbourne &amp; surrounds</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Company contact page; CoM waste providers list</t>
         </is>
@@ -1316,25 +1368,30 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>Yes (RORO / skip truck)</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
           <t>Melbourne (Dandenong, Somerton etc.)</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Company contact page; CoM list</t>
         </is>
@@ -1371,12 +1428,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1386,10 +1443,15 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Company website</t>
         </is>
@@ -1426,12 +1488,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1441,10 +1503,15 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Company website</t>
         </is>
@@ -1481,12 +1548,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1496,10 +1563,15 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>~60% of Melbourne</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Company contact page</t>
         </is>
@@ -1536,12 +1608,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1551,10 +1623,15 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>Company contact page</t>
         </is>
@@ -1591,12 +1668,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1606,10 +1683,15 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>East &amp; SE Melbourne</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Company contact page (email as published)</t>
         </is>
@@ -1646,25 +1728,30 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
           <t>Garden waste disposal offered</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>Company contact page</t>
         </is>
@@ -1701,12 +1788,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1716,10 +1803,15 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>~15km radius of Ringwood</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>No public email found after deep search; phone/office only (03 8872 7879)</t>
         </is>
@@ -1756,25 +1848,30 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
           <t>Yes (hooklift)</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
           <t>Organics / food organics</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>Melbourne &amp; Brisbane</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>No public general email found; use phone 1300 219 001 or online form</t>
         </is>
@@ -1811,7 +1908,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1821,15 +1918,20 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>Melbourne (also Sydney/Brisbane/Adelaide)</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Also admin@simplexwastesolutions.com; CoM list</t>
         </is>
@@ -1866,25 +1968,30 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
           <t>Yes (240L / 660L commercial)</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
           <t>All Melbourne (conditions apply)</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>Company website; CoM list</t>
         </is>
@@ -1921,25 +2028,30 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
           <t>Yes (commercial)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>LinkedIn / CoM list</t>
         </is>
@@ -1976,7 +2088,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1986,15 +2098,20 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
           <t>Organics available</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>Melbourne &amp; Geelong</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>Also bookings@speediewaste.com.au; CoM list</t>
         </is>
@@ -2031,25 +2148,30 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
           <t>Yes (collections)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>Metro Melbourne &amp; beyond</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Also service@binboy.com.au; CoM list</t>
         </is>
@@ -2086,25 +2208,30 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
           <t>Yes (wheelie bins)</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Garden tidy / green focus</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>Western suburbs Melbourne</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>Company website; CoM list</t>
         </is>
@@ -2141,12 +2268,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2156,10 +2283,15 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
           <t>Inner city &amp; CBD</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>No public email found; phone only 03 9824 1975</t>
         </is>
@@ -2196,25 +2328,30 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
           <t>Commercial waste services</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Yes (commercial)</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Organics (commercial)</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>Melbourne Metro (commercial only)</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>Company contact page; CoM list</t>
         </is>
@@ -2251,12 +2388,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Outer East / Yarra Ranges</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2266,10 +2403,15 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
           <t>Outer east Melbourne / surrounds</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Company contact page</t>
         </is>
@@ -2306,7 +2448,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -2316,15 +2458,20 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
           <t>Melbourne metro</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>Also sales@cscwaste.com.au; CoM list</t>
         </is>
@@ -2361,25 +2508,30 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
           <t>Yes (scheduled collections)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
           <t>East &amp; SE Melbourne</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Company contact page; CoM list (Elite Recycling)</t>
         </is>
@@ -2399,7 +2551,7 @@
           <t>1300 550 408</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>contact@wastewise.com.au</t>
         </is>
@@ -2416,25 +2568,30 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
           <t>Yes (commercial)</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Organics available</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>Also sales@wastewise.com.au on older site page | was: Company contact page; CoM list</t>
         </is>
@@ -2471,25 +2628,30 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>Mornington Peninsula / Melbourne</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
           <t>Yes (bags alternative)</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>No / N/A</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Yes – garden waste bags</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Melbourne metro</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Croc Bags garden &amp; general; company about page</t>
         </is>
@@ -2509,7 +2671,7 @@
           <t>1300 586 548</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>info@aussieskipbags.com.au</t>
         </is>
@@ -2526,25 +2688,30 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
           <t>Skip bag alternative</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>No / N/A</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>Yes – garden &amp; general skip bags</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>All Melbourne metro</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>Also operations@aussieskipbags.com.au | was: Also collects Croc Bags; company site</t>
         </is>
@@ -2581,25 +2748,30 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
           <t>Yes (MGBs)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
           <t>Bayside &amp; Melbourne</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Company website; CoM list</t>
         </is>
@@ -2636,7 +2808,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2646,15 +2818,20 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
           <t>Organics available</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>Australia incl. Melbourne</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>Company contact page</t>
         </is>
@@ -2691,7 +2868,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2701,15 +2878,20 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>Organics available</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Melbourne &amp; Australia</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>No public general email; use 13 13 39 or online enquiry form</t>
         </is>
@@ -2729,7 +2911,7 @@
           <t>13 29 55</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>cx.service@anz.veolia.com</t>
         </is>
@@ -2746,7 +2928,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2756,15 +2938,20 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
           <t>Garden / organics streams</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>Melbourne &amp; Australia</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>Customer experience team email from Veolia ANZ portals page; also call 13 29 55 | was: CoM waste providers list</t>
         </is>
@@ -2801,7 +2988,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2811,15 +2998,20 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Company website</t>
         </is>
@@ -2839,7 +3031,7 @@
           <t>13 15 46</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>jimscontracts@jims.net</t>
         </is>
@@ -2856,25 +3048,30 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
           <t>Check with franchisee</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Green waste skips</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>Melbourne suburbs (franchise network)</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="L43" s="3" t="inlineStr">
         <is>
           <t>Jim's Contracts / national office email; local franchisees may differ — also call 13 15 46 | was: Franchise model; local franchisees vary</t>
         </is>
@@ -2911,25 +3108,30 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Check with company</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>Organic recycling</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Melbourne CBD &amp; metro</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Company website; CoM list</t>
         </is>
@@ -2949,7 +3151,7 @@
           <t>1300 922 732 / 0476 306 181</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>info@waarec.com.au</t>
         </is>
@@ -2966,25 +3168,30 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
           <t>Yes (240L–1100L)</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>Food &amp; organic waste</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>Company website; CoM list</t>
         </is>
@@ -3021,25 +3228,30 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
           <t>Yes (hook lift)</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>Organics</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Company / LinkedIn; CoM list</t>
         </is>
@@ -3076,25 +3288,30 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
           <t>General / construction waste</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>Company contact; CoM list (Atlas Recycling)</t>
         </is>
@@ -3131,12 +3348,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3146,10 +3363,15 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Also sales@cleanway.com.au</t>
         </is>
@@ -3186,25 +3408,30 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
           <t>Green waste skips</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>Metro Melbourne</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="L49" s="3" t="inlineStr">
         <is>
           <t>Referral aggregator — no public email on site; phone 0482 392 415</t>
         </is>
@@ -3224,7 +3451,7 @@
           <t>03 9670 4042</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>admin@phoenixwastecollection.com.au</t>
         </is>
@@ -3241,14 +3468,14 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
           <t>Yes (listed under landfill)</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
           <t>Check with company</t>
@@ -3256,10 +3483,15 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>Company contact page; also phone 03 9670 4042 | was: City of Melbourne waste providers list</t>
         </is>
@@ -3279,7 +3511,7 @@
           <t>1300 292 783</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>sales@awaste.com.au</t>
         </is>
@@ -3296,25 +3528,30 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
           <t>Yes (listed)</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>Yes (listed recycling streams)</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="L51" s="3" t="inlineStr">
         <is>
           <t>Also known as AWASTE; Wyndham directory + company site | was: City of Melbourne waste providers list</t>
         </is>
@@ -3334,7 +3571,7 @@
           <t>1300 267 4696</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>contactcentre@coriowm.com.au</t>
         </is>
@@ -3351,25 +3588,30 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
+          <t>Geelong / Melbourne West &amp; SE</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
           <t>Yes (listed)</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>Organics (listed)</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>Geelong &amp; Melbourne surrounds</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>Also sales@coriowm.com.au; serves Geelong, Ballarat &amp; Melbourne | was: CoM list (phone shown as 1300 267 4696 on CoM; verify digit count)</t>
         </is>
@@ -3406,7 +3648,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -3416,15 +3658,20 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
           <t>Organics</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>Brand largely under Veolia; use 131 335 / Veolia channels; no separate public email found</t>
         </is>
@@ -3444,7 +3691,7 @@
           <t>1300 723 232</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>info@waynecleaningsystems.com.au</t>
         </is>
@@ -3461,25 +3708,30 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>Listed provider</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>Yes (listed streams)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>Company website contact | was: City of Melbourne waste providers list</t>
         </is>
@@ -3499,7 +3751,7 @@
           <t>1300 954 576</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>peter@limitlessrecycling.com.au</t>
         </is>
@@ -3516,25 +3768,30 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
           <t>Listed provider</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>Yes (listed)</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="L55" s="3" t="inlineStr">
         <is>
           <t>Recycling Near You directory listing | was: City of Melbourne waste providers list</t>
         </is>
@@ -3571,14 +3828,14 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
           <t>Yes (listed)</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
           <t>Check with company</t>
@@ -3586,10 +3843,15 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>No public email found; phone only 0406 267 275</t>
         </is>
@@ -3609,7 +3871,7 @@
           <t>0452 458 909</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>estimatorvic@aldcorporate.com.au</t>
         </is>
@@ -3626,14 +3888,14 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
           <t>Yes (construction waste)</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
           <t>Check with company</t>
@@ -3641,10 +3903,15 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="L57" s="3" t="inlineStr">
         <is>
           <t>Expert Demo site lists ALD Corporate VIC estimator email — confirm before outreach; phone 0452 458 909 from CoM list | was: City of Melbourne construction waste providers</t>
         </is>
@@ -3681,14 +3948,14 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
+          <t>Melbourne metro / surrounds</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
           <t>Yes (construction)</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Check with company</t>
-        </is>
-      </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
           <t>Check with company</t>
@@ -3696,10 +3963,15 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>No public email on site; phone 1300 307 450 / 0416 416 224 or online form — https://revertgroup.com.au/</t>
         </is>
@@ -3719,7 +3991,7 @@
           <t>1300 648 088</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>info@wasteninja.com.au</t>
         </is>
@@ -3736,7 +4008,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Melbourne metro / surrounds</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
@@ -3746,15 +4018,20 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
           <t>Food organics (listed)</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>Melbourne</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="L59" s="3" t="inlineStr">
         <is>
           <t>Company contact page | was: City of Melbourne food organics providers</t>
         </is>
@@ -3791,12 +4068,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>ACT (reference only — not VIC)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Check with company</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3806,17 +4083,2602 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
           <t>Canberra / ACT (NOT Melbourne)</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>User example URL; appears Canberra-based, included for reference only</t>
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Geelong All Bins</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>03 5277 1007</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>bookings@geelongallbins.com.au</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>https://geelongallbins.com.au/</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>26-27 Nepean Close, North Geelong VIC 3215</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Geelong / Bellarine</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Green waste accepted</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Greater Geelong, Torquay, Ocean Grove, Lara</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>EPA approved recycler; company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>SnapBin Hire</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>0408 521 806</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>info@snapbinhire.com.au</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>https://snapbinhire.com.au/</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Moolap, VIC</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Geelong / Bellarine</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Geelong</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Bin Hire Geelong</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>03 5214 2709</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>info@binhiregeelong.com.au</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>https://binhiregeelong.com.au/</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Gheringhap St, Geelong VIC 3220</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Geelong / Bellarine</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Geelong region</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Transformer Bin Hire (Geelong)</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>03 4242 4759</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>northshorerecycling16@gmail.com</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>https://transformerbinhire.com.au/</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Geelong VIC 3220</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Geelong / Bellarine</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Geelong</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Also linked to North Shore Recycling</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Skip Bin Hire Ballarat (Transformer)</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>03 4313 4727</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>info@skipbinhireballarat.com.au</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>https://skipbinhireballarat.com.au/</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat VIC 3350</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat / Central Highlands</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Greater Ballarat, Wendouree, Daylesford, Sebastopol</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat Budget Bin Hire</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>0417 358 734</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>budgetbinsballarat@bigpond.com</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ballaratbudgetbin.com.au/</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat VIC 3356</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat / Central Highlands</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat, Daylesford, Ballan, Maryborough &amp; surrounds</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat Skip Hire</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>0435 763 433</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>phil@ballaratskiphire.com.au</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>https://ballaratskiphire.com.au/</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat VIC</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat / Central Highlands</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Whitey's Skip Bins Bendigo</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>0417 870 824</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call)</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>https://whiteysskipbins.com.au/</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo VIC</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo / Loddon</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Company website — email not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Budget Bins Bendigo</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>0448 811 291</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call / book online)</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.budgetbinsbendigo.com.au/</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo VIC</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo / Loddon</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Green waste bins</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo &amp; Castlemaine</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Bin Planet</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>0494 101 747</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>callum@binplanet.com.au</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>https://binplanet.com.au/</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo / Victoria</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo / statewide</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo, Melbourne, Yarra Valley &amp; VIC</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>J.J. Richards — Bendigo East</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>03 5442 5378</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>operations.melbourne@jjswaste.com.au</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>https://jjrichards.com.au/</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>5-11 Piper Lane, East Bendigo VIC 3550</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo / Loddon</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Bendigo</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>JJ Richards regional depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>J.J. Richards — Ballarat</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>03 4436 6800</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>operations.bendigo@jjswaste.com.au</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>https://jjrichards.com.au/</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>28 Grandlee Drive, Wendouree VIC 3355</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat / Central Highlands</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Ballarat</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>JJ Richards regional depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Payless Skips Mildura</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>0458 729 537</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>payless.skips@bigpond.com</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.paylessskips.com.au/</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>PO Box 878, Merbein VIC 3505</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Mildura / NW Victoria</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Green / landscaping waste</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Mildura &amp; surrounds</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>J.J. Richards — Mildura</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>03 5022 4100</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>operations.mildura@jjswaste.com.au</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>https://jjrichards.com.au/</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>1 Silver City Hwy, Mourquong NSW 2739 (serves Mildura)</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Mildura / NW Victoria</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Mildura region</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>JJ Richards regional depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Delta Recycling — Latrobe Valley &amp; Gippsland</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>03 5174 9821</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>recycling@deltagroup.com.au</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.deltarecycling.com.au/</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>25 Hotham Street, Traralgon VIC 3844</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Gippsland / Latrobe Valley</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Yes (via Delta/SKIPZ network)</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Latrobe Valley &amp; Gippsland</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Also Melbourne Sunshine &amp; Port Melbourne sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Delta Recycling — Head Office / Port Melbourne</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>03 9646 8277</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>delta@deltagroup.com.au</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>https://www.deltarecycling.com.au/</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>577 Plummer Street, Port Melbourne VIC 3207</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne metro</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne &amp; VIC</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Parent of SKIPZ network</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Delta Recycling — Sunshine</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>03 9315 2555</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>recycling@deltagroup.com.au</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.deltarecycling.com.au/</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>473 Somerville Road, Sunshine VIC 3020</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne West</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne West</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Company contact page</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Goulburn Valley Skip Hire</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>03 5827 1372</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>admin@gvskips.com.au</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.goulburnvalleyskiphire.com.au/</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Shepparton VIC</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Shepparton / Goulburn Valley</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Shepparton &amp; surrounds</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Bins2u Shepparton</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>03 5823 2626</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call)</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>https://bins2u.com.au/</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Shepparton VIC</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Shepparton / Goulburn Valley</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Greater Shepparton &amp; surrounds</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Fast n Easy Skip Bin Hire</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>0415 515 536</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>fneskips@gmail.com</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fneskips.com.au/</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Greater Shepparton VIC</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Shepparton / Goulburn Valley</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Shepparton, Kialla, Mooroopna, Tatura &amp; more</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Binit Skips Echuca</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>0437 724 646</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>hire@binitskips.com</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>https://binitskips.com/</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Lockington / Echuca VIC</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Echuca / Murray</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Echuca, Moama &amp; surrounds</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Naish Waste Wangaratta</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>03 5721 4714</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call)</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>https://miniskips.net.au/skip-bins-waste-management-wangaratta-947/</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Wangaratta VIC</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>NE Victoria / Wangaratta</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Yes (front lift)</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>Garden &amp; green waste bins</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>Wangaratta, Rutherglen, Beechworth, Benalla, Chiltern</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Directory / Naish Waste listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>J.J. Richards — Wangaratta</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>03 5721 4714</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>admin.wodonga@jjswaste.com.au</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>https://jjrichards.com.au/</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>13-15 Kerr Street, Wangaratta VIC 3678</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>NE Victoria / Wangaratta</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>Wangaratta</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>JJ Richards regional depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>J.J. Richards — Wodonga</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>02 6056 3444</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>admin.wodonga@jjswaste.com.au</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>https://jjrichards.com.au/</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>3 Bullock Court, Wodonga VIC 3690</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Wodonga / Border</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>Wodonga / Albury region</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>JJ Richards regional depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Bartons Waste Collection</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>1800 012 212</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>info@bartonswaste.com</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>https://bartonswaste.com/</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Warrnambool VIC</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Warrnambool / SW Victoria</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>Warrnambool &amp; surrounds</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn / company listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Wheelie Waste</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>03 5562 0847 / 1800 999 690</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>admin@wheeliewaste.com.au</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>https://wheeliewaste.com.au/</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Warrnambool / Allansford VIC</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Warrnambool / SW Victoria</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Yes (clean-up bins)</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>Green waste</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>Warrnambool region / council services</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Also councilrequests@wheeliewaste.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Macc Waste Bin Hire</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>0499 881 099</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>info@maccwastebinhire.com.au</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>https://maccwastebinhire.com.au/</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>8 Glenville Drive, Melton VIC 3337</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne West / Melton</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>Melton / Melbourne West</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Company contact page</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Huss Industries (Huss Waste)</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>0450 035 035</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>info@husswaste.com.au</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>https://husswaste.com.au/</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>10 Dib Ct, Tullamarine VIC 3043</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne North / Tullamarine</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>Most of Melbourne</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Cheap Bin Hire &amp; Recycling</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>0414 401 111</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>info@cheapbinhire.com.au</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>https://cheapbinhire.com.au/</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Ravenhall VIC</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne West</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn / company site</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>D.C. Waste Management</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>03 9308 5488</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>accounts@dcwaste.com.au</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dcwaste.com.au/</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>189 Northbourne Road, Campbellfield VIC 3061</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne North</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Company site (also linked Bison Demolition mail@bisondemolitiongroup.com.au)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Rubbish Skip Hire (RSH)</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>1300 300 565</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>info@rubbishskiphire.com.au</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubbishskiphire.com.au/</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>39 Salvator Dr, Campbellfield VIC 3061</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne North</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>Green waste</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Ascot Bin Hire (Sycle)</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>0417 531 009</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>info@sycle.com.au</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>https://ascotbinhire.com.au/</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>2 Tube Street, Sunshine North VIC 3020</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne West</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne metro</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Now part of Sycle; accounts 03 9312 2991</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Sycle</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>0417 531 009</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>info@sycle.com.au</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>https://sycle.com.au/</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Sunshine North / Avalon / Fyansford VIC</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne / Geelong</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne &amp; Geelong (Fyansford/Avalon hubs)</t>
+        </is>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>Resource recovery + Ascot Bin Hire</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>SKIPBINEXPERTS</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>0404 039 988</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>skipbinexperts@gmail.com</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>https://skipbinexperts.com.au/</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Frankston / Melbourne suburbs</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Frankston / SE Melbourne</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>Garden waste</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>Frankston &amp; Melbourne suburbs</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Local Skip Bin Hire</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>1300 778 978</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>info@localskipbinhire.com</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.localskipbinhire.com/</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>National platform (AU); services VIC postcodes</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Victoria (multi-region platform)</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>Frankston, Mornington Peninsula &amp; VIC postcodes</t>
+        </is>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>Comparison/booking platform — Always You Pty Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Aussi Skips</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>0429 086 219</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>info@aussieskips.com.au</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>https://aussiskips.com.au/</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne VIC</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne metro</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>Also info@aussiskips.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Solo Resource Recovery</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>1300 467 656</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call / form)</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>https://solo.com.au/</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Australia (services Victoria)</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Victoria / national</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>Organics often available</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>Victoria &amp; national</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>Major waste operator; verify VIC desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>REMONDIS Australia</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>1300 073 666</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call / form)</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>https://remondis.com.au/</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Australia (services Victoria)</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Victoria / national</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>Organics often available</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>Victoria &amp; national</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>Major waste operator; verify local VIC contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>BookaBin (Victoria network)</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>See site / supplier network</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Not published (online booking)</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bookabin.com.au/victoria-skip-bins.aspx</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>National skip bin booking network</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Victoria (multi-region platform)</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>No / N/A</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>Via suppliers</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>Victoria postcodes via supplier network</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace connecting to local skip suppliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Visy Recycling</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>1300 368 479</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call)</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>https://www.visy.com.au/</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Australia (major VIC operations)</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Victoria / national</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Yes (recycling streams)</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>Victoria / national</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>City of Melbourne paper/cardboard providers list</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Iron Mountain (secure destruction)</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>1300 476 668</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call)</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ironmountain.com/au</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne / Victoria</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>No / N/A</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Secure destruction collections</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne / VIC</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>CoM mixed recycling list — secure docs focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Shred-X Secure Destruction</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>1300 747 339</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call)</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>https://www.shred-x.com.au/</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne / Victoria</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>No / N/A</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Secure destruction</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne / VIC</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>CoM secure destruction providers</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Organic Matters Environmental Services</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>0403 320 580</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Not found publicly (call)</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Search Organic Matters Environmental Melbourne</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne VIC</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne metro</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>Check with company</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Organics collections</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>Food organics</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>City of Melbourne food organics providers</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K60"/>
+  <autoFilter ref="A1:L103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3827,212 +6689,119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Waste Expo Australia 2026 — WasteVantage invite email</t>
+          <t>Victoria waste / skip / rearlift / garden bag companies — expanded list</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Event</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Compiled / updated</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Waste Expo Australia</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Dates</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>28 – 29 October 2026, 9am – 5pm</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total companies</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Venue</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Melbourne Convention and Exhibition Centre (MCEC), South Wharf</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>With public email</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Expo website</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.wasteexpoaustralia.com.au/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>WasteVantage</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://ihublogistics.com/wastevantage/</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>New in this expansion</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Coverage</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>SUBJECT (option 1)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{{Company Name}} — meet WasteVantage at Waste Expo Australia (28–29 Oct)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>SUBJECT (option 2)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Invitation: see WasteVantage live at Waste Expo Melbourne, 28–29 October</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Melbourne metro + West/North/East/SE, Geelong/Bellarine, Ballarat, Bendigo, Mildura, Shepparton, Echuca, Wangaratta/Wodonga, Warrnambool, Gippsland/Latrobe</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Legend</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>EMAIL BODY — copy below</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="520" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hi {{First Name / team at Company Name}},
-We're writing from WasteVantage to invite you to visit us at Waste Expo Australia 2026.
-When: Wednesday 28 – Thursday 29 October 2026, 9am–5pm
-Where: Melbourne Convention and Exhibition Centre (MCEC)
-Event: https://www.wasteexpoaustralia.com.au/
-Waste Expo is Australia's leading gathering for waste, recycling and resource recovery — with 3,500+ attendees, 140+ exhibitors and free education sessions. It's the best place this year to see what's next for operators like yours.
-WHY VISIT WASTEVANTAGE AT THE EXPO?
-WasteVantage is purpose-built waste management software for Australian and New Zealand operators — including skip bin hire, rearlift / wheelie bin rounds, front lift, and garden / skip bag style services.
-At our stand you can:
-• See a live demo of bookings, dispatch, bin tracking and driver run sheets in one system
-• Talk through your operation (skip delivery/pickup, rearlift schedules, garden bag collections) with people who understand the workflow
-• Compare how you run today vs automating pricing, job scheduling, customer SMS and same-day invoicing
-• Ask about Xero / MYOB / Stripe integrations so office admin and cash flow stay connected
-• Get a clear view of whether WasteVantage fits a single-stream business or a multi-stream fleet (skips + rearlift + bags)
-WHAT WASTEVANTAGE CAN DO FOR {{Company Name}}
-If you're juggling phone bookings, spreadsheets, drivers and invoices, the expo is a low-risk way to see how operators are cutting admin and missed jobs:
-• High volume skip deliveries, pickups and swaps → Smart scheduling &amp; dispatch so jobs aren't missed or double-booked
-• "Where is that bin?" / lost assets → Real-time bin status, location and customer tracking
-• Drivers needing paper run sheets and constant office calls → Automated run sheets on driver phones + live job updates
-• Slow or messy invoicing after jobs close → One-click / same-day invoicing synced to Xero or MYOB
-• Customers chasing ETAs → Automated SMS / notifications and clearer service proof
-• Growing into rearlift or garden bags alongside skips → One platform for multi-stream operations
-Built and supported in Australia for local operators — not a generic overseas logistics tool bolted onto waste.
-WHY COME IN PERSON?
-• Free trade visitor registration for industry professionals via the expo site
-• Face-to-face demo beats a cold website click — bring your toughest operational question
-• See peers and suppliers in one venue while you're there
-• Melbourne timing — ideal if you already service metro Melbourne and surrounds
-If you're free on either day, we'd love 15–20 minutes at our stand to walk you through a demo tailored to skip / rearlift / garden bag work.
-RSVP / book a time: reply to this email with a preferred day (28 or 29 Oct) and we'll hold a slot for {{Company Name}}.
-Expo info &amp; visitor registration: https://www.wasteexpoaustralia.com.au/
-Learn more about WasteVantage: https://ihublogistics.com/wastevantage/
-Looking forward to meeting you in Melbourne.
-Kind regards,
-{{Your Name}}
-{{Your Title}}
-WasteVantage
-{{Your Phone}}
-{{Your Email}}
-https://ihublogistics.com/wastevantage/
-</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Green rows = newly added in Victoria expansion pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Yellow email cells = no public email found (use phone / web form)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>SHORT FOLLOW-UP SUBJECT</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Quick reminder — WasteVantage at Waste Expo (28–29 Oct)</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Still not exhaustive</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>SHORT FOLLOW-UP BODY</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="160" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Hi {{First Name}},
-Just a short follow-up on our invite to meet at Waste Expo Australia, 28–29 October 2026 at MCEC Melbourne.
-We'll be showing WasteVantage live — bookings, bin tracking, driver apps and automated invoicing for skip, rearlift and garden bag operators.
-If you're attending, reply with your preferred day and we'll book a 15-minute demo for {{Company Name}}.
-Expo: https://www.wasteexpoaustralia.com.au/
-Thanks,
-{{Your Name}} | WasteVantage</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>SENDING TIPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>1. Replace {{Company Name}} / {{First Name}} from the company list sheet.  2. Add booth/stand number once confirmed.  3. Send one-to-one (not bulk BCC).  4. Confirm exhibitor registration &amp; free visitor entry before promising it.</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>This is an expanded Victoria list focused on skip/rearlift/garden-bag style operators — not every waste company in VIC (e.g. every tiny regional tip contractor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sources: company websites, City of Melbourne waste providers, JJ Richards depot list, regional operator sites.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A12:B12"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4043,304 +6812,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Melbourne &amp; surrounds waste / skip / rearlift / garden bag companies</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Compiled date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Total companies listed</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>With public email found</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>With phone found</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Primary sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1. Company websites / contact pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2. City of Melbourne – Your guide to waste providers (https://www.melbourne.vic.gov.au/waste-providers)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3. Web search of skip bin hire, rearlift, garden bag operators in Melbourne VIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>- Yellow Pages listings were blocked/misrouted for this agent session; contacts were taken from company sites and the CoM directory instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>- Kong Skip Bins (user example) appears to operate in Canberra/ACT, not Melbourne — included for reference only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>- Yellow cells in Email column = public email not found; phone/website still usable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>- Service flags are based on published information; confirm capability/pricing directly with each operator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>- This list is for research/outreach; not an endorsement. Verify details before use as contacts change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Email enrichment update</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Newly filled emails: 13; still missing public email: 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unlimited Bins (Skip Hire Melbourne)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>admin@unlimitedbins.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Choice Bins</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>info@choicebins.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Waste Wise Environmental</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>contact@wastewise.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Aussie Skip Bags</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>info@aussieskipbags.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Veolia Environmental Services</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>cx.service@anz.veolia.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Jim's Skip Bins</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>jimscontracts@jims.net</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Phoenix Environmental Waste</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>admin@phoenixwastecollection.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Australian Waste Management</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sales@awaste.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Corio Waste Management</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>contactcentre@coriowm.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Wayne Cleaning Systems</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>info@waynecleaningsystems.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Limitless Secure Recycling &amp; Waste Solutions</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>peter@limitlessrecycling.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Expert Demo</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>estimatorvic@aldcorporate.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Waste Ninja</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>info@wasteninja.com.au</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Green email cells = newly found in this enrichment pass. Yellow = still no public email (use phone).</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>See also: research/WasteExpo_2026_WasteVantage_Invite_Email.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Full invite email Word document is in the research folder.</t>
         </is>
       </c>
     </row>
